--- a/product_surveys/020_fuel_pump_control_module_survey--product_surveys.xlsx
+++ b/product_surveys/020_fuel_pump_control_module_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,10 +548,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fuel Pump Control Module Information</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How often do you use the Fuel Pump Control Module?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please select a frequency</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,14 +575,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fuel Pump Control Module Selection</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Please select a Fuel Pump Control Module from the list</t>
-        </is>
-      </c>
+          <t>What inspired you to select this Fuel Pump Control Module?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -598,10 +598,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fuel Pump Control Module Selection</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How would you rate the performance of the Fuel Pump Control Module?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please select from the options</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -611,7 +615,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -621,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fuel Pump Control Module Selection</t>
+          <t>Do you have any suggestions for improving the Fuel Pump Control Module?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,7 +638,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -644,7 +648,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fuel Pump Control Module Selection</t>
+          <t>Have you experienced any issues with the Fuel Pump Control Module?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,7 +661,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -667,7 +671,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fuel Pump Control Module Selection</t>
+          <t>What do you think about the overall quality of the Fuel Pump Control Module?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,7 +684,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -690,20 +694,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fuel Pump Control Module Selection</t>
+          <t>How would you rate the fuel efficiency of the Fuel Pump Control Module?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -713,7 +717,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fuel Pump Control Module Selection</t>
+          <t>What was the reason for the selection?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,7 +730,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -736,14 +740,10 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How did you select the Fuel Pump Control Module?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Please explain</t>
-        </is>
-      </c>
+          <t>How often will the Fuel Pump Control Module be used?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -763,7 +763,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What was the reason for the selection?</t>
+          <t>How would you rate the value of the Fuel Pump Control Module?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -776,7 +776,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -786,310 +786,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>How often will the Fuel Pump Control Module be used?</t>
+          <t>Do you have any other comments?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What do you think about this product?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>How would you rate this product?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Do you have any other comments?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1106,12 +807,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="49" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1134,51 +835,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fuel_pump_control_module_survey_page_3_choices</t>
+          <t>fuel_pump_control_module_survey_page_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fuel_pump_control_module_survey_page_3_choices</t>
+          <t>fuel_pump_control_module_survey_page_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fuel_pump_control_module_survey_page_3_choices</t>
+          <t>fuel_pump_control_module_survey_page_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1190,12 +891,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1207,12 +908,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1224,301 +925,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fuel_pump_control_module_survey_page_5_choices</t>
+          <t>fuel_pump_control_module_survey_page_10_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'option_1'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Option 1'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fuel_pump_control_module_survey_page_5_choices</t>
+          <t>fuel_pump_control_module_survey_page_10_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'option_2'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Option 2'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fuel_pump_control_module_survey_page_5_choices</t>
+          <t>fuel_pump_control_module_survey_page_10_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'option_3'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Option 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_6_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_6_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_7_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_7_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_8_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_9_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_9_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'frequently'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Frequently'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'occasionally'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Occasionally'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'rarely'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Rarely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'good'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>fuel_pump_control_module_survey_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'poor'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'Poor'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
